--- a/src/test/resources/Exceltestdata/ExcelTestdata.xlsx
+++ b/src/test/resources/Exceltestdata/ExcelTestdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rakhy\eclipse-workspace-new\DS_algo_project\src\test\resources\Exceltestdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A00628-61B2-4A62-93FD-614CAB980862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2EB0A4-E41F-4CF8-A2AB-DA257F353114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
